--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -107,7 +107,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>穷奇</t>
+    <t>青龙</t>
   </si>
   <si>
     <t>1载</t>
@@ -131,22 +131,22 @@
     <t>10</t>
   </si>
   <si>
-    <t>穷奇幻象</t>
-  </si>
-  <si>
-    <t>穷奇镜像</t>
+    <t>青龙幻象</t>
+  </si>
+  <si>
+    <t>青龙分身</t>
   </si>
   <si>
     <t>1003</t>
   </si>
   <si>
-    <t>穷奇分身</t>
+    <t>青龙法相</t>
   </si>
   <si>
     <t>2001</t>
   </si>
   <si>
-    <t>穷奇法相</t>
+    <t>青龙化身</t>
   </si>
   <si>
     <t>3001,3002</t>
@@ -1709,7 +1709,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G3 H3 I3 J3 K3 L3 N3:P3 Q3 R3:T3 U3:V3 C4:D4 E4 F4:G4 H4 I4 J4 K4 L4 O4:P4 Q4 R4:T4 U4:V4 C5:G5 H5 I5 J5 K5 L5 O5:P5 Q5 R5:T5 U5:V5 M3:M5 N4:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L3 C4:L5 M3:V5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -44,6 +44,12 @@
     <t>MonsterName</t>
   </si>
   <si>
+    <t>LoseRate</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>Attr</t>
   </si>
   <si>
@@ -77,12 +83,21 @@
     <t>CritRate</t>
   </si>
   <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
     <t>CritRateResist</t>
   </si>
   <si>
     <t>CritDamageResist</t>
   </si>
   <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
     <t>Protect</t>
   </si>
   <si>
@@ -125,34 +140,43 @@
     <t>1亿</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>1001,3001</t>
+  </si>
+  <si>
+    <t>10,100000000</t>
   </si>
   <si>
     <t>青龙幻象</t>
   </si>
   <si>
+    <t>1001,1004,1007</t>
+  </si>
+  <si>
+    <t>20,20,20</t>
+  </si>
+  <si>
     <t>青龙分身</t>
   </si>
   <si>
-    <t>1003</t>
+    <t>2002,2007,2008,2009</t>
+  </si>
+  <si>
+    <t>20,20,20,20</t>
   </si>
   <si>
     <t>青龙法相</t>
   </si>
   <si>
-    <t>2001</t>
+    <t>1002,2009,2007,1009</t>
   </si>
   <si>
     <t>青龙化身</t>
   </si>
   <si>
-    <t>3001,3002</t>
-  </si>
-  <si>
-    <t>100,10</t>
+    <t>1004,2009,2007,2002,1001</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20</t>
   </si>
 </sst>
 </file>
@@ -810,10 +834,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -1136,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:V15"/>
+  <dimension ref="C1:AA15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -1144,23 +1168,28 @@
     <col min="3" max="4" width="9.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.0833333333333" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.8333333333333" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.0833333333333" style="4" customWidth="1"/>
-    <col min="13" max="14" width="11.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8.66666666666667" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.41666666666667" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.6666666666667" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5833333333333" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" customWidth="1"/>
-    <col min="23" max="16346" width="9" style="1"/>
-    <col min="16347" max="16383" width="9" style="5"/>
-    <col min="16384" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="7.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.0833333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8" style="4" customWidth="1"/>
+    <col min="14" max="14" width="11" style="4" customWidth="1"/>
+    <col min="15" max="15" width="11.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.41666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5833333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.25" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="9.375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="21.25" style="1" customWidth="1"/>
+    <col min="27" max="27" width="14" style="1" customWidth="1"/>
+    <col min="28" max="16313" width="9" style="1"/>
+    <col min="16314" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="3:4">
@@ -1171,7 +1200,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:27">
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1232,10 +1261,25 @@
       <c r="V3" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="W3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:27">
       <c r="C4" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1294,70 +1338,100 @@
       <c r="V4" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="W4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:22">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:27">
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:22">
+    <row r="6" customHeight="1" spans="3:27">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1368,58 +1442,73 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.1</v>
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1">
+        <v>200</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J6" s="8">
         <v>0.1</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>28</v>
+      <c r="K6" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="L6" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="8">
         <v>2</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="2">
+      <c r="O6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="2">
         <v>2</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" s="2">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="S6" s="2">
         <v>10000</v>
       </c>
-      <c r="R6" s="2">
+      <c r="T6" s="2">
         <v>10000</v>
       </c>
-      <c r="S6" s="2">
+      <c r="U6" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V6" s="2">
         <v>5000</v>
       </c>
-      <c r="T6" s="2">
+      <c r="W6" s="2">
+        <v>100</v>
+      </c>
+      <c r="X6" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y6" s="2">
         <v>99</v>
       </c>
-      <c r="U6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>32</v>
+      <c r="Z6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:22">
+    <row r="7" customHeight="1" spans="3:27">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1430,58 +1519,73 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0.1</v>
+        <v>38</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1">
+        <v>250</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J7" s="8">
         <v>0.1</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>28</v>
+      <c r="K7" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="L7" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="8">
         <v>2</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="O7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="2">
         <v>2</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" s="2">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>10000</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>10000</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V7" s="2">
         <v>5000</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
+        <v>100</v>
+      </c>
+      <c r="X7" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y7" s="2">
         <v>99</v>
       </c>
-      <c r="U7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" s="11" t="s">
-        <v>32</v>
+      <c r="Z7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:22">
+    <row r="8" customHeight="1" spans="3:27">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1492,58 +1596,73 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0.1</v>
+        <v>41</v>
+      </c>
+      <c r="G8" s="1">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1">
+        <v>300</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J8" s="8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>28</v>
+      <c r="K8" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="L8" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="8">
         <v>2</v>
       </c>
-      <c r="M8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="O8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="2">
         <v>2</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" s="2">
         <v>0.1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="S8" s="2">
         <v>10000</v>
       </c>
-      <c r="R8" s="2">
+      <c r="T8" s="2">
         <v>10000</v>
       </c>
-      <c r="S8" s="2">
+      <c r="U8" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V8" s="2">
         <v>5000</v>
       </c>
-      <c r="T8" s="2">
+      <c r="W8" s="2">
+        <v>100</v>
+      </c>
+      <c r="X8" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y8" s="2">
         <v>99</v>
       </c>
-      <c r="U8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>32</v>
+      <c r="Z8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:22">
+    <row r="9" customHeight="1" spans="3:27">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1554,58 +1673,73 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0.1</v>
+        <v>44</v>
+      </c>
+      <c r="G9" s="1">
+        <v>35</v>
+      </c>
+      <c r="H9" s="1">
+        <v>350</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J9" s="8">
         <v>0.1</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>28</v>
+      <c r="K9" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="L9" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="8">
         <v>2</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="2">
+      <c r="O9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="2">
         <v>2</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" s="2">
         <v>0.1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="S9" s="2">
         <v>10000</v>
       </c>
-      <c r="R9" s="2">
+      <c r="T9" s="2">
         <v>10000</v>
       </c>
-      <c r="S9" s="2">
+      <c r="U9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V9" s="2">
         <v>5000</v>
       </c>
-      <c r="T9" s="2">
+      <c r="W9" s="2">
+        <v>100</v>
+      </c>
+      <c r="X9" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y9" s="2">
         <v>99</v>
       </c>
-      <c r="U9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" s="11" t="s">
-        <v>32</v>
+      <c r="Z9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:22">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:27">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1616,100 +1750,115 @@
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0.1</v>
+        <v>46</v>
+      </c>
+      <c r="G10" s="2">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>400</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J10" s="8">
         <v>0.1</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>28</v>
+      <c r="K10" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="L10" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="8">
         <v>2</v>
       </c>
-      <c r="M10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="O10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="2">
         <v>2</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" s="2">
+      <c r="Q10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" s="2">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="S10" s="2">
         <v>10000</v>
       </c>
-      <c r="R10" s="2">
+      <c r="T10" s="2">
         <v>10000</v>
       </c>
-      <c r="S10" s="2">
+      <c r="U10" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V10" s="2">
         <v>5000</v>
       </c>
-      <c r="T10" s="2">
+      <c r="W10" s="2">
+        <v>100</v>
+      </c>
+      <c r="X10" s="2">
+        <v>50</v>
+      </c>
+      <c r="Y10" s="2">
         <v>99</v>
       </c>
-      <c r="U10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>40</v>
+      <c r="Z10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="7:12">
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="9:14">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="7:12">
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="9:14">
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="7:12">
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="9:14">
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="7:12">
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="9:14">
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="7:12">
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="9:14">
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L3 C4:L5 M3:V5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -1454,13 +1454,13 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L6" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>33</v>
@@ -1478,7 +1478,7 @@
         <v>35</v>
       </c>
       <c r="R6" s="2">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S6" s="2">
         <v>10000</v>
@@ -1531,13 +1531,13 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>33</v>
@@ -1555,7 +1555,7 @@
         <v>35</v>
       </c>
       <c r="R7" s="2">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S7" s="2">
         <v>10000</v>
@@ -1608,13 +1608,13 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>33</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="R8" s="2">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S8" s="2">
         <v>10000</v>
@@ -1685,13 +1685,13 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>33</v>
@@ -1709,7 +1709,7 @@
         <v>35</v>
       </c>
       <c r="R9" s="2">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S9" s="2">
         <v>10000</v>
@@ -1762,13 +1762,13 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="8">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>33</v>
@@ -1786,7 +1786,7 @@
         <v>35</v>
       </c>
       <c r="R10" s="2">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="S10" s="2">
         <v>10000</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <t>青龙幻象</t>
   </si>
   <si>
-    <t>1001,1004,1007</t>
+    <t>1002,1004,1007</t>
   </si>
   <si>
     <t>20,20,20</t>
@@ -1454,13 +1454,13 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L6" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>33</v>
@@ -1472,13 +1472,13 @@
         <v>34</v>
       </c>
       <c r="P6" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R6" s="2">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S6" s="2">
         <v>10000</v>
@@ -1493,7 +1493,7 @@
         <v>5000</v>
       </c>
       <c r="W6" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X6" s="2">
         <v>50</v>
@@ -1531,13 +1531,13 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>33</v>
@@ -1549,13 +1549,13 @@
         <v>34</v>
       </c>
       <c r="P7" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R7" s="2">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S7" s="2">
         <v>10000</v>
@@ -1570,7 +1570,7 @@
         <v>5000</v>
       </c>
       <c r="W7" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X7" s="2">
         <v>50</v>
@@ -1608,13 +1608,13 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>33</v>
@@ -1626,13 +1626,13 @@
         <v>34</v>
       </c>
       <c r="P8" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R8" s="2">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S8" s="2">
         <v>10000</v>
@@ -1647,7 +1647,7 @@
         <v>5000</v>
       </c>
       <c r="W8" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X8" s="2">
         <v>50</v>
@@ -1685,13 +1685,13 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>33</v>
@@ -1703,13 +1703,13 @@
         <v>34</v>
       </c>
       <c r="P9" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R9" s="2">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S9" s="2">
         <v>10000</v>
@@ -1724,7 +1724,7 @@
         <v>5000</v>
       </c>
       <c r="W9" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X9" s="2">
         <v>50</v>
@@ -1762,13 +1762,13 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>33</v>
@@ -1780,13 +1780,13 @@
         <v>34</v>
       </c>
       <c r="P10" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R10" s="2">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="S10" s="2">
         <v>10000</v>
@@ -1801,7 +1801,7 @@
         <v>5000</v>
       </c>
       <c r="W10" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X10" s="2">
         <v>50</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -125,31 +125,31 @@
     <t>青龙</t>
   </si>
   <si>
+    <t>1穰</t>
+  </si>
+  <si>
+    <t>1秭</t>
+  </si>
+  <si>
     <t>1载</t>
   </si>
   <si>
-    <t>1正</t>
-  </si>
-  <si>
-    <t>1恒</t>
-  </si>
-  <si>
     <t>1兆</t>
   </si>
   <si>
-    <t>1亿</t>
-  </si>
-  <si>
-    <t>1001,3001</t>
-  </si>
-  <si>
-    <t>10,100000000</t>
+    <t>1万</t>
+  </si>
+  <si>
+    <t>1002,3001,1008</t>
+  </si>
+  <si>
+    <t>20,100000000,20</t>
   </si>
   <si>
     <t>青龙幻象</t>
   </si>
   <si>
-    <t>1002,1004,1007</t>
+    <t>1001,1004,1007</t>
   </si>
   <si>
     <t>20,20,20</t>
@@ -1445,7 +1445,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>200</v>
@@ -1454,37 +1454,37 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L6" s="8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N6" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P6" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R6" s="2">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="S6" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="T6" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="U6" s="2">
         <v>10000</v>
@@ -1522,7 +1522,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="1">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
         <v>250</v>
@@ -1531,37 +1531,37 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N7" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P7" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R7" s="2">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="S7" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="T7" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="U7" s="2">
         <v>10000</v>
@@ -1599,7 +1599,7 @@
         <v>41</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1">
         <v>300</v>
@@ -1608,37 +1608,37 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N8" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P8" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R8" s="2">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="S8" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="T8" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="U8" s="2">
         <v>10000</v>
@@ -1676,7 +1676,7 @@
         <v>44</v>
       </c>
       <c r="G9" s="1">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H9" s="1">
         <v>350</v>
@@ -1685,37 +1685,37 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N9" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P9" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R9" s="2">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="S9" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="T9" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="U9" s="2">
         <v>10000</v>
@@ -1753,7 +1753,7 @@
         <v>46</v>
       </c>
       <c r="G10" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2">
         <v>400</v>
@@ -1762,37 +1762,37 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N10" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P10" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="R10" s="2">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="S10" s="2">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="T10" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="U10" s="2">
         <v>10000</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -134,7 +134,7 @@
     <t>1载</t>
   </si>
   <si>
-    <t>1兆</t>
+    <t>1京</t>
   </si>
   <si>
     <t>1万</t>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -1454,7 +1454,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
@@ -1531,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
@@ -1608,7 +1608,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
@@ -1685,7 +1685,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
@@ -1762,7 +1762,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1454,25 +1454,25 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L6" s="8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N6" s="8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P6" s="2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>35</v>
@@ -1531,25 +1531,25 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N7" s="8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P7" s="2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>35</v>
@@ -1608,25 +1608,25 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N8" s="8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P8" s="2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>35</v>
@@ -1685,25 +1685,25 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N9" s="8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P9" s="2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>35</v>
@@ -1762,25 +1762,25 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N10" s="8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>34</v>
       </c>
       <c r="P10" s="2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>35</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1454,7 +1454,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="8">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>32</v>
@@ -1472,7 +1472,7 @@
         <v>34</v>
       </c>
       <c r="P6" s="2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>35</v>
@@ -1531,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="8">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>32</v>
@@ -1549,7 +1549,7 @@
         <v>34</v>
       </c>
       <c r="P7" s="2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>35</v>
@@ -1608,7 +1608,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="8">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>32</v>
@@ -1626,7 +1626,7 @@
         <v>34</v>
       </c>
       <c r="P8" s="2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>35</v>
@@ -1685,7 +1685,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="8">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>32</v>
@@ -1703,7 +1703,7 @@
         <v>34</v>
       </c>
       <c r="P9" s="2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>35</v>
@@ -1762,7 +1762,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="8">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>32</v>
@@ -1780,7 +1780,7 @@
         <v>34</v>
       </c>
       <c r="P10" s="2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>35</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -125,19 +125,19 @@
     <t>青龙</t>
   </si>
   <si>
-    <t>1穰</t>
-  </si>
-  <si>
     <t>1秭</t>
   </si>
   <si>
-    <t>1载</t>
-  </si>
-  <si>
-    <t>1京</t>
-  </si>
-  <si>
-    <t>1万</t>
+    <t>1垓</t>
+  </si>
+  <si>
+    <t>1正</t>
+  </si>
+  <si>
+    <t>1兆</t>
+  </si>
+  <si>
+    <t>1000</t>
   </si>
   <si>
     <t>1002,3001,1008</t>
@@ -1474,7 +1474,7 @@
       <c r="P6" s="2">
         <v>1.3</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R6" s="2">
@@ -1551,7 +1551,7 @@
       <c r="P7" s="2">
         <v>1.3</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R7" s="2">
@@ -1628,7 +1628,7 @@
       <c r="P8" s="2">
         <v>1.3</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R8" s="2">
@@ -1705,7 +1705,7 @@
       <c r="P9" s="2">
         <v>1.3</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R9" s="2">
@@ -1782,7 +1782,7 @@
       <c r="P10" s="2">
         <v>1.3</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R10" s="2">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -95,9 +95,15 @@
     <t>Accuracy</t>
   </si>
   <si>
+    <t>AccuracyRise</t>
+  </si>
+  <si>
     <t>Miss</t>
   </si>
   <si>
+    <t>MissRise</t>
+  </si>
+  <si>
     <t>Protect</t>
   </si>
   <si>
@@ -177,6 +183,33 @@
   </si>
   <si>
     <t>20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>白虎</t>
+  </si>
+  <si>
+    <t>1沟</t>
+  </si>
+  <si>
+    <t>1穰</t>
+  </si>
+  <si>
+    <t>1极</t>
+  </si>
+  <si>
+    <t>1000亿</t>
+  </si>
+  <si>
+    <t>白虎幻象</t>
+  </si>
+  <si>
+    <t>白虎分身</t>
+  </si>
+  <si>
+    <t>白虎法相</t>
+  </si>
+  <si>
+    <t>白虎化身</t>
   </si>
 </sst>
 </file>
@@ -1160,36 +1193,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA15"/>
+  <dimension ref="C1:AC17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.0833333333333" style="4" customWidth="1"/>
+    <col min="3" max="4" width="9.87610619469027" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2477876106195" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6283185840708" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6283185840708" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.6283185840708" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.0796460176991" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="4" customWidth="1"/>
     <col min="13" max="13" width="8" style="4" customWidth="1"/>
     <col min="14" max="14" width="11" style="4" customWidth="1"/>
-    <col min="15" max="15" width="11.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.66666666666667" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.41666666666667" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5833333333333" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.25" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.5" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.25" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="21.25" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14" style="1" customWidth="1"/>
-    <col min="28" max="16313" width="9" style="1"/>
-    <col min="16314" max="16384" width="9" style="5"/>
+    <col min="15" max="15" width="11.5044247787611" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.12389380530973" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.66371681415929" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.41592920353982" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.6283185840708" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.87610619469027" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5840707964602" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.24778761061947" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5044247787611" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.76991150442478" style="1" customWidth="1"/>
+    <col min="25" max="26" width="9.24778761061947" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.3716814159292" style="1" customWidth="1"/>
+    <col min="28" max="28" width="21.2477876106195" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14" style="1" customWidth="1"/>
+    <col min="30" max="16315" width="9" style="1"/>
+    <col min="16316" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="3:4">
@@ -1200,7 +1234,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1276,10 +1310,16 @@
       <c r="AA3" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="AB3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C4" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1353,85 +1393,97 @@
       <c r="AA4" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="AB4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C5" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="S5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="T5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="U5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="7" t="s">
+      <c r="V5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R5" s="7" t="s">
+      <c r="W5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="X5" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:27">
+    <row r="6" customHeight="1" spans="3:29">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1442,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -1451,31 +1503,31 @@
         <v>200</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J6" s="8">
         <v>1.24</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L6" s="8">
         <v>1.1</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N6" s="8">
         <v>1.45</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P6" s="2">
         <v>1.3</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R6" s="2">
         <v>1.05</v>
@@ -1496,19 +1548,25 @@
         <v>200</v>
       </c>
       <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
         <v>50</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
         <v>99</v>
       </c>
-      <c r="Z6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA6" s="11" t="s">
-        <v>37</v>
+      <c r="AB6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:27">
+    <row r="7" customHeight="1" spans="3:29">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1519,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>90</v>
@@ -1528,31 +1586,31 @@
         <v>250</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="8">
         <v>1.24</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L7" s="8">
         <v>1.1</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N7" s="8">
         <v>1.45</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P7" s="2">
         <v>1.3</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R7" s="2">
         <v>1.05</v>
@@ -1573,19 +1631,25 @@
         <v>200</v>
       </c>
       <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
         <v>50</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
         <v>99</v>
       </c>
-      <c r="Z7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA7" s="11" t="s">
-        <v>40</v>
+      <c r="AB7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:27">
+    <row r="8" customHeight="1" spans="3:29">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1596,7 +1660,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1">
         <v>80</v>
@@ -1605,31 +1669,31 @@
         <v>300</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="8">
         <v>1.24</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" s="8">
         <v>1.1</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N8" s="8">
         <v>1.45</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P8" s="2">
         <v>1.3</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R8" s="2">
         <v>1.05</v>
@@ -1650,19 +1714,25 @@
         <v>200</v>
       </c>
       <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
         <v>50</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
         <v>99</v>
       </c>
-      <c r="Z8" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>43</v>
+      <c r="AB8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:27">
+    <row r="9" customHeight="1" spans="3:29">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1673,7 +1743,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1">
         <v>70</v>
@@ -1682,31 +1752,31 @@
         <v>350</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" s="8">
         <v>1.24</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L9" s="8">
         <v>1.1</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N9" s="8">
         <v>1.45</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P9" s="2">
         <v>1.3</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R9" s="2">
         <v>1.05</v>
@@ -1727,19 +1797,25 @@
         <v>200</v>
       </c>
       <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
         <v>50</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
         <v>99</v>
       </c>
-      <c r="Z9" s="11" t="s">
+      <c r="AB9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AA9" s="11" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:27">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1750,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2">
         <v>60</v>
@@ -1759,31 +1835,31 @@
         <v>400</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" s="8">
         <v>1.24</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L10" s="8">
         <v>1.1</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N10" s="8">
         <v>1.45</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P10" s="2">
         <v>1.3</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R10" s="2">
         <v>1.05</v>
@@ -1804,16 +1880,22 @@
         <v>200</v>
       </c>
       <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
         <v>50</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
         <v>99</v>
       </c>
-      <c r="Z10" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>48</v>
+      <c r="AB10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="9:14">
@@ -1824,41 +1906,432 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="9:14">
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C12" s="2">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>200</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="S12" s="2">
+        <v>600</v>
+      </c>
+      <c r="T12" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U12" s="2">
+        <v>20000</v>
+      </c>
+      <c r="V12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W12" s="2">
+        <v>300</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="9:14">
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C13" s="2">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="1">
+        <v>90</v>
+      </c>
+      <c r="H13" s="1">
+        <v>250</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R13" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="S13" s="2">
+        <v>600</v>
+      </c>
+      <c r="T13" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U13" s="2">
+        <v>20000</v>
+      </c>
+      <c r="V13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W13" s="2">
+        <v>300</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="9:14">
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C14" s="2">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="1">
+        <v>80</v>
+      </c>
+      <c r="H14" s="1">
+        <v>300</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="S14" s="2">
+        <v>600</v>
+      </c>
+      <c r="T14" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U14" s="2">
+        <v>20000</v>
+      </c>
+      <c r="V14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W14" s="2">
+        <v>300</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="9:14">
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C15" s="2">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="1">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1">
+        <v>350</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="S15" s="2">
+        <v>600</v>
+      </c>
+      <c r="T15" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U15" s="2">
+        <v>20000</v>
+      </c>
+      <c r="V15" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W15" s="2">
+        <v>300</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C16" s="2">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="2">
+        <v>60</v>
+      </c>
+      <c r="H16" s="2">
+        <v>400</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="S16" s="2">
+        <v>600</v>
+      </c>
+      <c r="T16" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U16" s="2">
+        <v>20000</v>
+      </c>
+      <c r="V16" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W16" s="2">
+        <v>300</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="9:14">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="X3 Z3 X4 Z4 X5 Z5 Y3:Y5 C3:W5 AA3:AC5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -210,6 +210,30 @@
   </si>
   <si>
     <t>白虎化身</t>
+  </si>
+  <si>
+    <t>朱雀</t>
+  </si>
+  <si>
+    <t>1涧</t>
+  </si>
+  <si>
+    <t>1恒</t>
+  </si>
+  <si>
+    <t>1000兆</t>
+  </si>
+  <si>
+    <t>朱雀幻象</t>
+  </si>
+  <si>
+    <t>朱雀分身</t>
+  </si>
+  <si>
+    <t>朱雀法相</t>
+  </si>
+  <si>
+    <t>朱雀化身</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AC17"/>
+  <dimension ref="C1:AC23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.87610619469027" style="1" customWidth="1"/>
@@ -1212,7 +1236,7 @@
     <col min="16" max="16" width="7.12389380530973" style="1" customWidth="1"/>
     <col min="17" max="17" width="8.66371681415929" style="1" customWidth="1"/>
     <col min="18" max="18" width="8.41592920353982" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.6283185840708" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6902654867257" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.87610619469027" style="1" customWidth="1"/>
     <col min="21" max="21" width="11.5840707964602" style="1" customWidth="1"/>
     <col min="22" max="22" width="9.24778761061947" style="1" customWidth="1"/>
@@ -2329,9 +2353,432 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C18" s="2">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>200</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P18" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R18" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="S18" s="2">
+        <v>8000</v>
+      </c>
+      <c r="T18" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U18" s="2">
+        <v>25000</v>
+      </c>
+      <c r="V18" s="2">
+        <v>15000</v>
+      </c>
+      <c r="W18" s="2">
+        <v>400</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C19" s="2">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="1">
+        <v>90</v>
+      </c>
+      <c r="H19" s="1">
+        <v>250</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="S19" s="2">
+        <v>8000</v>
+      </c>
+      <c r="T19" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U19" s="2">
+        <v>25000</v>
+      </c>
+      <c r="V19" s="2">
+        <v>15000</v>
+      </c>
+      <c r="W19" s="2">
+        <v>400</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C20" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="1">
+        <v>80</v>
+      </c>
+      <c r="H20" s="1">
+        <v>300</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P20" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="S20" s="2">
+        <v>8000</v>
+      </c>
+      <c r="T20" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U20" s="2">
+        <v>25000</v>
+      </c>
+      <c r="V20" s="2">
+        <v>15000</v>
+      </c>
+      <c r="W20" s="2">
+        <v>400</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC20" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C21" s="2">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="1">
+        <v>70</v>
+      </c>
+      <c r="H21" s="1">
+        <v>350</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P21" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R21" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="S21" s="2">
+        <v>8000</v>
+      </c>
+      <c r="T21" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U21" s="2">
+        <v>25000</v>
+      </c>
+      <c r="V21" s="2">
+        <v>15000</v>
+      </c>
+      <c r="W21" s="2">
+        <v>400</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C22" s="2">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="2">
+        <v>60</v>
+      </c>
+      <c r="H22" s="2">
+        <v>400</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1.24</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N22" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="S22" s="2">
+        <v>8000</v>
+      </c>
+      <c r="T22" s="2">
+        <v>6000</v>
+      </c>
+      <c r="U22" s="2">
+        <v>25000</v>
+      </c>
+      <c r="V22" s="2">
+        <v>15000</v>
+      </c>
+      <c r="W22" s="2">
+        <v>400</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC22" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="9:14">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="X3 Z3 X4 Z4 X5 Z5 Y3:Y5 C3:W5 AA3:AC5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AC5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -1572,13 +1572,13 @@
         <v>200</v>
       </c>
       <c r="X6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y6" s="2">
         <v>50</v>
       </c>
       <c r="Z6" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA6" s="2">
         <v>99</v>
@@ -1655,13 +1655,13 @@
         <v>200</v>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y7" s="2">
         <v>50</v>
       </c>
       <c r="Z7" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA7" s="2">
         <v>99</v>
@@ -1738,13 +1738,13 @@
         <v>200</v>
       </c>
       <c r="X8" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y8" s="2">
         <v>50</v>
       </c>
       <c r="Z8" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA8" s="2">
         <v>99</v>
@@ -1821,13 +1821,13 @@
         <v>200</v>
       </c>
       <c r="X9" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y9" s="2">
         <v>50</v>
       </c>
       <c r="Z9" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA9" s="2">
         <v>99</v>
@@ -1904,13 +1904,13 @@
         <v>200</v>
       </c>
       <c r="X10" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y10" s="2">
         <v>50</v>
       </c>
       <c r="Z10" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA10" s="2">
         <v>99</v>
@@ -1995,7 +1995,7 @@
         <v>300</v>
       </c>
       <c r="X12" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Y12" s="2">
         <v>75</v>
@@ -2078,7 +2078,7 @@
         <v>300</v>
       </c>
       <c r="X13" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Y13" s="2">
         <v>75</v>
@@ -2161,7 +2161,7 @@
         <v>300</v>
       </c>
       <c r="X14" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Y14" s="2">
         <v>75</v>
@@ -2244,7 +2244,7 @@
         <v>300</v>
       </c>
       <c r="X15" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Y15" s="2">
         <v>75</v>
@@ -2327,7 +2327,7 @@
         <v>300</v>
       </c>
       <c r="X16" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Y16" s="2">
         <v>75</v>
@@ -2376,7 +2376,7 @@
         <v>61</v>
       </c>
       <c r="J18" s="8">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>52</v>
@@ -2424,7 +2424,7 @@
         <v>100</v>
       </c>
       <c r="Z18" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AA18" s="2">
         <v>99</v>
@@ -2459,7 +2459,7 @@
         <v>61</v>
       </c>
       <c r="J19" s="8">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>52</v>
@@ -2507,7 +2507,7 @@
         <v>100</v>
       </c>
       <c r="Z19" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AA19" s="2">
         <v>99</v>
@@ -2542,7 +2542,7 @@
         <v>61</v>
       </c>
       <c r="J20" s="8">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>52</v>
@@ -2590,7 +2590,7 @@
         <v>100</v>
       </c>
       <c r="Z20" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AA20" s="2">
         <v>99</v>
@@ -2625,7 +2625,7 @@
         <v>61</v>
       </c>
       <c r="J21" s="8">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>52</v>
@@ -2673,7 +2673,7 @@
         <v>100</v>
       </c>
       <c r="Z21" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="2">
         <v>99</v>
@@ -2708,7 +2708,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="8">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>52</v>
@@ -2756,7 +2756,7 @@
         <v>100</v>
       </c>
       <c r="Z22" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AA22" s="2">
         <v>99</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -234,6 +234,24 @@
   </si>
   <si>
     <t>朱雀化身</t>
+  </si>
+  <si>
+    <t>玄武</t>
+  </si>
+  <si>
+    <t>1阿</t>
+  </si>
+  <si>
+    <t>玄武幻象</t>
+  </si>
+  <si>
+    <t>玄武分身</t>
+  </si>
+  <si>
+    <t>玄武法相</t>
+  </si>
+  <si>
+    <t>玄武化身</t>
   </si>
 </sst>
 </file>
@@ -1217,34 +1235,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AC23"/>
+  <dimension ref="C1:AC29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.87610619469027" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.2477876106195" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6283185840708" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6283185840708" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.6283185840708" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.0796460176991" style="4" customWidth="1"/>
+    <col min="3" max="4" width="9.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.0833333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="4" customWidth="1"/>
     <col min="13" max="13" width="8" style="4" customWidth="1"/>
     <col min="14" max="14" width="11" style="4" customWidth="1"/>
-    <col min="15" max="15" width="11.5044247787611" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.12389380530973" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.66371681415929" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.41592920353982" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6902654867257" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.87610619469027" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5840707964602" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.5044247787611" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8.76991150442478" style="1" customWidth="1"/>
-    <col min="25" max="26" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.3716814159292" style="1" customWidth="1"/>
-    <col min="28" max="28" width="21.2477876106195" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5083333333333" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.41666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6916666666667" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5833333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.25" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5083333333333" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.76666666666667" style="1" customWidth="1"/>
+    <col min="25" max="26" width="9.25" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="21.25" style="1" customWidth="1"/>
     <col min="29" max="29" width="14" style="1" customWidth="1"/>
     <col min="30" max="16315" width="9" style="1"/>
     <col min="16316" max="16384" width="9" style="5"/>
@@ -2776,6 +2794,429 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C24" s="2">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="1">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>200</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N24" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R24" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S24" s="2">
+        <v>16000</v>
+      </c>
+      <c r="T24" s="2">
+        <v>12000</v>
+      </c>
+      <c r="U24" s="2">
+        <v>40000</v>
+      </c>
+      <c r="V24" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W24" s="2">
+        <v>600</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC24" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C25" s="2">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="1">
+        <v>90</v>
+      </c>
+      <c r="H25" s="1">
+        <v>250</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N25" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S25" s="2">
+        <v>16000</v>
+      </c>
+      <c r="T25" s="2">
+        <v>12000</v>
+      </c>
+      <c r="U25" s="2">
+        <v>40000</v>
+      </c>
+      <c r="V25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W25" s="2">
+        <v>600</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C26" s="2">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="1">
+        <v>80</v>
+      </c>
+      <c r="H26" s="1">
+        <v>300</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N26" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S26" s="2">
+        <v>16000</v>
+      </c>
+      <c r="T26" s="2">
+        <v>12000</v>
+      </c>
+      <c r="U26" s="2">
+        <v>40000</v>
+      </c>
+      <c r="V26" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W26" s="2">
+        <v>600</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC26" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C27" s="2">
+        <v>19</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="1">
+        <v>70</v>
+      </c>
+      <c r="H27" s="1">
+        <v>350</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P27" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R27" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S27" s="2">
+        <v>16000</v>
+      </c>
+      <c r="T27" s="2">
+        <v>12000</v>
+      </c>
+      <c r="U27" s="2">
+        <v>40000</v>
+      </c>
+      <c r="V27" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W27" s="2">
+        <v>600</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C28" s="2">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="2">
+        <v>60</v>
+      </c>
+      <c r="H28" s="2">
+        <v>400</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J28" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N28" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R28" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S28" s="2">
+        <v>16000</v>
+      </c>
+      <c r="T28" s="2">
+        <v>12000</v>
+      </c>
+      <c r="U28" s="2">
+        <v>40000</v>
+      </c>
+      <c r="V28" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W28" s="2">
+        <v>600</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z28" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>99</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC28" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="9:14">
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AC5" errorStyle="warning">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -239,19 +239,55 @@
     <t>玄武</t>
   </si>
   <si>
-    <t>1阿</t>
+    <t>1E+54</t>
+  </si>
+  <si>
+    <t>1E+48</t>
+  </si>
+  <si>
+    <t>1E+64</t>
+  </si>
+  <si>
+    <t>1E+36</t>
+  </si>
+  <si>
+    <t>1E+28</t>
+  </si>
+  <si>
+    <t>1002,1008,1012</t>
+  </si>
+  <si>
+    <t>20,100000000,20,20</t>
   </si>
   <si>
     <t>玄武幻象</t>
   </si>
   <si>
+    <t>1001,1004,1007,2012</t>
+  </si>
+  <si>
     <t>玄武分身</t>
   </si>
   <si>
+    <t>2002,2007,2008,2009,3012</t>
+  </si>
+  <si>
     <t>玄武法相</t>
   </si>
   <si>
+    <t>1002,2009,2007,1009,1012,2012</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20</t>
+  </si>
+  <si>
     <t>玄武化身</t>
+  </si>
+  <si>
+    <t>1004,2009,2007,2002,1001,1012,2012</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
   </si>
 </sst>
 </file>
@@ -916,6 +952,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2799,7 +2841,7 @@
         <v>16</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2813,35 +2855,35 @@
       <c r="H24" s="1">
         <v>200</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>54</v>
+      <c r="I24" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="J24" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>54</v>
+        <v>1.7</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="L24" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>69</v>
+        <v>1.4</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="N24" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P24" s="2">
         <v>1.7</v>
       </c>
-      <c r="O24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P24" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>53</v>
+      <c r="Q24" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="R24" s="2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S24" s="2">
         <v>16000</v>
@@ -2871,10 +2913,10 @@
         <v>99</v>
       </c>
       <c r="AB24" s="11" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="AC24" s="11" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -2882,13 +2924,13 @@
         <v>17</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G25" s="1">
         <v>90</v>
@@ -2896,35 +2938,35 @@
       <c r="H25" s="1">
         <v>250</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>54</v>
+      <c r="I25" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="J25" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>54</v>
+        <v>1.7</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="L25" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>69</v>
+        <v>1.4</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="N25" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P25" s="2">
         <v>1.7</v>
       </c>
-      <c r="O25" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P25" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>53</v>
+      <c r="Q25" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="R25" s="2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S25" s="2">
         <v>16000</v>
@@ -2954,10 +2996,10 @@
         <v>99</v>
       </c>
       <c r="AB25" s="11" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AC25" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -2965,13 +3007,13 @@
         <v>18</v>
       </c>
       <c r="D26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G26" s="1">
         <v>80</v>
@@ -2979,35 +3021,35 @@
       <c r="H26" s="1">
         <v>300</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>54</v>
+      <c r="I26" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="J26" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>54</v>
+        <v>1.7</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="L26" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>69</v>
+        <v>1.4</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="N26" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P26" s="2">
         <v>1.7</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P26" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q26" s="11" t="s">
-        <v>53</v>
+      <c r="Q26" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="R26" s="2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S26" s="2">
         <v>16000</v>
@@ -3037,10 +3079,10 @@
         <v>99</v>
       </c>
       <c r="AB26" s="11" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="AC26" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -3048,13 +3090,13 @@
         <v>19</v>
       </c>
       <c r="D27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G27" s="1">
         <v>70</v>
@@ -3062,35 +3104,35 @@
       <c r="H27" s="1">
         <v>350</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>54</v>
+      <c r="I27" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="J27" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>54</v>
+        <v>1.7</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="L27" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>69</v>
+        <v>1.4</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="N27" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P27" s="2">
         <v>1.7</v>
       </c>
-      <c r="O27" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P27" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q27" s="11" t="s">
-        <v>53</v>
+      <c r="Q27" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="R27" s="2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S27" s="2">
         <v>16000</v>
@@ -3120,10 +3162,10 @@
         <v>99</v>
       </c>
       <c r="AB27" s="11" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -3131,13 +3173,13 @@
         <v>20</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2">
         <v>60</v>
@@ -3145,35 +3187,35 @@
       <c r="H28" s="2">
         <v>400</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>54</v>
+      <c r="I28" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="J28" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>54</v>
+        <v>1.7</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="L28" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>69</v>
+        <v>1.4</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="N28" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P28" s="2">
         <v>1.7</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P28" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="Q28" s="11" t="s">
-        <v>53</v>
+      <c r="Q28" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="R28" s="2">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S28" s="2">
         <v>16000</v>
@@ -3203,10 +3245,10 @@
         <v>99</v>
       </c>
       <c r="AB28" s="11" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="9:14">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="87">
   <si>
     <t>ID</t>
   </si>
@@ -245,13 +245,13 @@
     <t>1E+48</t>
   </si>
   <si>
-    <t>1E+64</t>
-  </si>
-  <si>
-    <t>1E+36</t>
-  </si>
-  <si>
-    <t>1E+28</t>
+    <t>1E+74</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>1E+30</t>
   </si>
   <si>
     <t>1002,1008,1012</t>
@@ -263,31 +263,34 @@
     <t>玄武幻象</t>
   </si>
   <si>
-    <t>1001,1004,1007,2012</t>
+    <t>1001,1004,1007,2012,1008</t>
   </si>
   <si>
     <t>玄武分身</t>
   </si>
   <si>
-    <t>2002,2007,2008,2009,3012</t>
+    <t>2002,2007,2008,2009,3012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20</t>
   </si>
   <si>
     <t>玄武法相</t>
   </si>
   <si>
-    <t>1002,2009,2007,1009,1012,2012</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20</t>
+    <t>1002,2009,2007,1009,1012,2012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
   </si>
   <si>
     <t>玄武化身</t>
   </si>
   <si>
-    <t>1004,2009,2007,2002,1001,1012,2012</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20</t>
+    <t>1004,2009,2007,2002,1001,1012,2012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1307,7 @@
     <col min="24" max="24" width="8.76666666666667" style="1" customWidth="1"/>
     <col min="25" max="26" width="9.25" style="1" customWidth="1"/>
     <col min="27" max="27" width="9.375" style="1" customWidth="1"/>
-    <col min="28" max="28" width="21.25" style="1" customWidth="1"/>
+    <col min="28" max="28" width="26.5" style="1" customWidth="1"/>
     <col min="29" max="29" width="14" style="1" customWidth="1"/>
     <col min="30" max="16315" width="9" style="1"/>
     <col min="16316" max="16384" width="9" style="5"/>
@@ -2853,7 +2856,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>69</v>
@@ -2871,7 +2874,7 @@
         <v>71</v>
       </c>
       <c r="N24" s="8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O24" s="13" t="s">
         <v>72</v>
@@ -2883,7 +2886,7 @@
         <v>73</v>
       </c>
       <c r="R24" s="2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S24" s="2">
         <v>16000</v>
@@ -2936,7 +2939,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="1">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>69</v>
@@ -2954,7 +2957,7 @@
         <v>71</v>
       </c>
       <c r="N25" s="8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O25" s="13" t="s">
         <v>72</v>
@@ -2966,7 +2969,7 @@
         <v>73</v>
       </c>
       <c r="R25" s="2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S25" s="2">
         <v>16000</v>
@@ -2999,7 +3002,7 @@
         <v>77</v>
       </c>
       <c r="AC25" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -3018,8 +3021,8 @@
       <c r="G26" s="1">
         <v>80</v>
       </c>
-      <c r="H26" s="1">
-        <v>300</v>
+      <c r="H26" s="2">
+        <v>400</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>69</v>
@@ -3037,7 +3040,7 @@
         <v>71</v>
       </c>
       <c r="N26" s="8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="13" t="s">
         <v>72</v>
@@ -3049,7 +3052,7 @@
         <v>73</v>
       </c>
       <c r="R26" s="2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S26" s="2">
         <v>16000</v>
@@ -3082,7 +3085,7 @@
         <v>79</v>
       </c>
       <c r="AC26" s="11" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -3096,13 +3099,13 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" s="1">
         <v>70</v>
       </c>
-      <c r="H27" s="1">
-        <v>350</v>
+      <c r="H27" s="2">
+        <v>400</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>69</v>
@@ -3120,7 +3123,7 @@
         <v>71</v>
       </c>
       <c r="N27" s="8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O27" s="13" t="s">
         <v>72</v>
@@ -3132,7 +3135,7 @@
         <v>73</v>
       </c>
       <c r="R27" s="2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S27" s="2">
         <v>16000</v>
@@ -3162,10 +3165,10 @@
         <v>99</v>
       </c>
       <c r="AB27" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC27" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:29">
@@ -3179,7 +3182,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G28" s="2">
         <v>60</v>
@@ -3203,7 +3206,7 @@
         <v>71</v>
       </c>
       <c r="N28" s="8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="13" t="s">
         <v>72</v>
@@ -3215,7 +3218,7 @@
         <v>73</v>
       </c>
       <c r="R28" s="2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S28" s="2">
         <v>16000</v>
@@ -3245,10 +3248,10 @@
         <v>99</v>
       </c>
       <c r="AB28" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC28" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="9:14">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>ID</t>
   </si>
@@ -80,6 +80,12 @@
     <t>StrongRise</t>
   </si>
   <si>
+    <t>Parray</t>
+  </si>
+  <si>
+    <t>ParrayRise</t>
+  </si>
+  <si>
     <t>CritRate</t>
   </si>
   <si>
@@ -251,46 +257,55 @@
     <t>1E+40</t>
   </si>
   <si>
+    <t>1E+20</t>
+  </si>
+  <si>
+    <t>1E+1</t>
+  </si>
+  <si>
+    <t>1002,1008,1012</t>
+  </si>
+  <si>
+    <t>20,100000000,20,20</t>
+  </si>
+  <si>
+    <t>玄武幻象</t>
+  </si>
+  <si>
+    <t>1001,1004,1007,2012,1008</t>
+  </si>
+  <si>
+    <t>玄武分身</t>
+  </si>
+  <si>
+    <t>2002,2007,2008,2009,3012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>玄武法相</t>
+  </si>
+  <si>
+    <t>1002,2009,2007,1009,1012,2012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>玄武化身</t>
+  </si>
+  <si>
+    <t>1004,2009,2007,2002,1001,1012,2012,1008</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>1E+30</t>
-  </si>
-  <si>
-    <t>1002,1008,1012</t>
-  </si>
-  <si>
-    <t>20,100000000,20,20</t>
-  </si>
-  <si>
-    <t>玄武幻象</t>
-  </si>
-  <si>
-    <t>1001,1004,1007,2012,1008</t>
-  </si>
-  <si>
-    <t>玄武分身</t>
-  </si>
-  <si>
-    <t>2002,2007,2008,2009,3012,1008</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>玄武法相</t>
-  </si>
-  <si>
-    <t>1002,2009,2007,1009,1012,2012,1008</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20</t>
-  </si>
-  <si>
-    <t>玄武化身</t>
-  </si>
-  <si>
-    <t>1004,2009,2007,2002,1001,1012,2012,1008</t>
-  </si>
-  <si>
-    <t>20,20,20,20,20,20,20,20,20</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AC29"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -1298,19 +1313,19 @@
     <col min="15" max="15" width="11.5083333333333" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.125" style="1" customWidth="1"/>
     <col min="17" max="17" width="8.66666666666667" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.41666666666667" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6916666666667" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5833333333333" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.25" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.5083333333333" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8.76666666666667" style="1" customWidth="1"/>
-    <col min="25" max="26" width="9.25" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.375" style="1" customWidth="1"/>
-    <col min="28" max="28" width="26.5" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14" style="1" customWidth="1"/>
-    <col min="30" max="16315" width="9" style="1"/>
-    <col min="16316" max="16384" width="9" style="5"/>
+    <col min="18" max="20" width="8.41666666666667" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.6916666666667" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7.875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="11.5833333333333" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5083333333333" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8.76666666666667" style="1" customWidth="1"/>
+    <col min="27" max="28" width="9.25" style="1" customWidth="1"/>
+    <col min="29" max="29" width="9.375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="26.5" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14" style="1" customWidth="1"/>
+    <col min="32" max="16317" width="9" style="1"/>
+    <col min="16318" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="3:4">
@@ -1321,7 +1336,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1403,10 +1418,16 @@
       <c r="AC3" s="7" t="s">
         <v>26</v>
       </c>
+      <c r="AD3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C4" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1486,91 +1507,103 @@
       <c r="AC4" s="7" t="s">
         <v>26</v>
       </c>
+      <c r="AD4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="V5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="W5" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="X5" s="7" t="s">
         <v>30</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="AB5" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:29">
+    <row r="6" customHeight="1" spans="3:31">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1581,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -1590,70 +1623,76 @@
         <v>200</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J6" s="8">
         <v>1.24</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" s="8">
         <v>1.1</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N6" s="8">
         <v>1.45</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P6" s="2">
         <v>1.3</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R6" s="2">
         <v>1.05</v>
       </c>
       <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
         <v>400</v>
       </c>
-      <c r="T6" s="2">
+      <c r="V6" s="2">
         <v>4000</v>
       </c>
-      <c r="U6" s="2">
+      <c r="W6" s="2">
         <v>10000</v>
       </c>
-      <c r="V6" s="2">
+      <c r="X6" s="2">
         <v>5000</v>
       </c>
-      <c r="W6" s="2">
+      <c r="Y6" s="2">
         <v>200</v>
       </c>
-      <c r="X6" s="2">
+      <c r="Z6" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AA6" s="2">
         <v>50</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AB6" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AC6" s="2">
         <v>99</v>
       </c>
-      <c r="AB6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC6" s="11" t="s">
-        <v>39</v>
+      <c r="AD6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:29">
+    <row r="7" customHeight="1" spans="3:31">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1664,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
         <v>90</v>
@@ -1673,70 +1712,76 @@
         <v>250</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J7" s="8">
         <v>1.24</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" s="8">
         <v>1.1</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N7" s="8">
         <v>1.45</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P7" s="2">
         <v>1.3</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R7" s="2">
         <v>1.05</v>
       </c>
       <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
         <v>400</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>4000</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>10000</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>5000</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>200</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>50</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>99</v>
       </c>
-      <c r="AB7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC7" s="11" t="s">
-        <v>42</v>
+      <c r="AD7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:29">
+    <row r="8" customHeight="1" spans="3:31">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1747,7 +1792,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1">
         <v>80</v>
@@ -1756,70 +1801,76 @@
         <v>300</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J8" s="8">
         <v>1.24</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" s="8">
         <v>1.1</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N8" s="8">
         <v>1.45</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P8" s="2">
         <v>1.3</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R8" s="2">
         <v>1.05</v>
       </c>
       <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
         <v>400</v>
       </c>
-      <c r="T8" s="2">
+      <c r="V8" s="2">
         <v>4000</v>
       </c>
-      <c r="U8" s="2">
+      <c r="W8" s="2">
         <v>10000</v>
       </c>
-      <c r="V8" s="2">
+      <c r="X8" s="2">
         <v>5000</v>
       </c>
-      <c r="W8" s="2">
+      <c r="Y8" s="2">
         <v>200</v>
       </c>
-      <c r="X8" s="2">
+      <c r="Z8" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="AA8" s="2">
         <v>50</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="AB8" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AC8" s="2">
         <v>99</v>
       </c>
-      <c r="AB8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC8" s="11" t="s">
-        <v>45</v>
+      <c r="AD8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:29">
+    <row r="9" customHeight="1" spans="3:31">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1830,7 +1881,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1">
         <v>70</v>
@@ -1839,70 +1890,76 @@
         <v>350</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J9" s="8">
         <v>1.24</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" s="8">
         <v>1.1</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N9" s="8">
         <v>1.45</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P9" s="2">
         <v>1.3</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R9" s="2">
         <v>1.05</v>
       </c>
       <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
         <v>400</v>
       </c>
-      <c r="T9" s="2">
+      <c r="V9" s="2">
         <v>4000</v>
       </c>
-      <c r="U9" s="2">
+      <c r="W9" s="2">
         <v>10000</v>
       </c>
-      <c r="V9" s="2">
+      <c r="X9" s="2">
         <v>5000</v>
       </c>
-      <c r="W9" s="2">
+      <c r="Y9" s="2">
         <v>200</v>
       </c>
-      <c r="X9" s="2">
+      <c r="Z9" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="AA9" s="2">
         <v>50</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="AB9" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AC9" s="2">
         <v>99</v>
       </c>
-      <c r="AB9" s="11" t="s">
+      <c r="AD9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AC9" s="11" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1913,7 +1970,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2">
         <v>60</v>
@@ -1922,67 +1979,73 @@
         <v>400</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J10" s="8">
         <v>1.24</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L10" s="8">
         <v>1.1</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N10" s="8">
         <v>1.45</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P10" s="2">
         <v>1.3</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R10" s="2">
         <v>1.05</v>
       </c>
       <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
         <v>400</v>
       </c>
-      <c r="T10" s="2">
+      <c r="V10" s="2">
         <v>4000</v>
       </c>
-      <c r="U10" s="2">
+      <c r="W10" s="2">
         <v>10000</v>
       </c>
-      <c r="V10" s="2">
+      <c r="X10" s="2">
         <v>5000</v>
       </c>
-      <c r="W10" s="2">
+      <c r="Y10" s="2">
         <v>200</v>
       </c>
-      <c r="X10" s="2">
+      <c r="Z10" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="AA10" s="2">
         <v>50</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AB10" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AC10" s="2">
         <v>99</v>
       </c>
-      <c r="AB10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>50</v>
+      <c r="AD10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="9:14">
@@ -1993,7 +2056,7 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C12" s="2">
         <v>6</v>
       </c>
@@ -2004,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G12" s="1">
         <v>100</v>
@@ -2013,70 +2076,76 @@
         <v>200</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J12" s="8">
         <v>1.24</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L12" s="8">
         <v>1.1</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N12" s="8">
         <v>1.55</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P12" s="2">
         <v>1.3</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R12" s="2">
         <v>1.05</v>
       </c>
       <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
         <v>600</v>
       </c>
-      <c r="T12" s="2">
+      <c r="V12" s="2">
         <v>6000</v>
       </c>
-      <c r="U12" s="2">
+      <c r="W12" s="2">
         <v>20000</v>
       </c>
-      <c r="V12" s="2">
+      <c r="X12" s="2">
         <v>10000</v>
       </c>
-      <c r="W12" s="2">
+      <c r="Y12" s="2">
         <v>300</v>
       </c>
-      <c r="X12" s="2">
+      <c r="Z12" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="AA12" s="2">
         <v>75</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="AB12" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AC12" s="2">
         <v>99</v>
       </c>
-      <c r="AB12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC12" s="11" t="s">
-        <v>39</v>
+      <c r="AD12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C13" s="2">
         <v>7</v>
       </c>
@@ -2087,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" s="1">
         <v>90</v>
@@ -2096,70 +2165,76 @@
         <v>250</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J13" s="8">
         <v>1.24</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L13" s="8">
         <v>1.1</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N13" s="8">
         <v>1.55</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P13" s="2">
         <v>1.3</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R13" s="2">
         <v>1.05</v>
       </c>
       <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
         <v>600</v>
       </c>
-      <c r="T13" s="2">
+      <c r="V13" s="2">
         <v>6000</v>
       </c>
-      <c r="U13" s="2">
+      <c r="W13" s="2">
         <v>20000</v>
       </c>
-      <c r="V13" s="2">
+      <c r="X13" s="2">
         <v>10000</v>
       </c>
-      <c r="W13" s="2">
+      <c r="Y13" s="2">
         <v>300</v>
       </c>
-      <c r="X13" s="2">
+      <c r="Z13" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y13" s="2">
+      <c r="AA13" s="2">
         <v>75</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="AB13" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AC13" s="2">
         <v>99</v>
       </c>
-      <c r="AB13" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC13" s="11" t="s">
-        <v>42</v>
+      <c r="AD13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C14" s="2">
         <v>8</v>
       </c>
@@ -2170,7 +2245,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1">
         <v>80</v>
@@ -2179,70 +2254,76 @@
         <v>300</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J14" s="8">
         <v>1.24</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L14" s="8">
         <v>1.1</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N14" s="8">
         <v>1.55</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P14" s="2">
         <v>1.3</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R14" s="2">
         <v>1.05</v>
       </c>
       <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
         <v>600</v>
       </c>
-      <c r="T14" s="2">
+      <c r="V14" s="2">
         <v>6000</v>
       </c>
-      <c r="U14" s="2">
+      <c r="W14" s="2">
         <v>20000</v>
       </c>
-      <c r="V14" s="2">
+      <c r="X14" s="2">
         <v>10000</v>
       </c>
-      <c r="W14" s="2">
+      <c r="Y14" s="2">
         <v>300</v>
       </c>
-      <c r="X14" s="2">
+      <c r="Z14" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="AA14" s="2">
         <v>75</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="AB14" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AC14" s="2">
         <v>99</v>
       </c>
-      <c r="AB14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC14" s="11" t="s">
-        <v>45</v>
+      <c r="AD14" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C15" s="2">
         <v>9</v>
       </c>
@@ -2253,7 +2334,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1">
         <v>70</v>
@@ -2262,70 +2343,76 @@
         <v>350</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J15" s="8">
         <v>1.24</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L15" s="8">
         <v>1.1</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N15" s="8">
         <v>1.55</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P15" s="2">
         <v>1.3</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R15" s="2">
         <v>1.05</v>
       </c>
       <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
         <v>600</v>
       </c>
-      <c r="T15" s="2">
+      <c r="V15" s="2">
         <v>6000</v>
       </c>
-      <c r="U15" s="2">
+      <c r="W15" s="2">
         <v>20000</v>
       </c>
-      <c r="V15" s="2">
+      <c r="X15" s="2">
         <v>10000</v>
       </c>
-      <c r="W15" s="2">
+      <c r="Y15" s="2">
         <v>300</v>
       </c>
-      <c r="X15" s="2">
+      <c r="Z15" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="AA15" s="2">
         <v>75</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="AB15" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AC15" s="2">
         <v>99</v>
       </c>
-      <c r="AB15" s="11" t="s">
+      <c r="AD15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE15" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AC15" s="11" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C16" s="2">
         <v>10</v>
       </c>
@@ -2336,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2">
         <v>60</v>
@@ -2345,67 +2432,73 @@
         <v>400</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J16" s="8">
         <v>1.24</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L16" s="8">
         <v>1.1</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N16" s="8">
         <v>1.55</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P16" s="2">
         <v>1.3</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R16" s="2">
         <v>1.05</v>
       </c>
       <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
         <v>600</v>
       </c>
-      <c r="T16" s="2">
+      <c r="V16" s="2">
         <v>6000</v>
       </c>
-      <c r="U16" s="2">
+      <c r="W16" s="2">
         <v>20000</v>
       </c>
-      <c r="V16" s="2">
+      <c r="X16" s="2">
         <v>10000</v>
       </c>
-      <c r="W16" s="2">
+      <c r="Y16" s="2">
         <v>300</v>
       </c>
-      <c r="X16" s="2">
+      <c r="Z16" s="2">
         <v>0.3</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="AA16" s="2">
         <v>75</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="AB16" s="2">
         <v>0.1</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AC16" s="2">
         <v>99</v>
       </c>
-      <c r="AB16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC16" s="11" t="s">
-        <v>50</v>
+      <c r="AD16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="9:14">
@@ -2416,7 +2509,7 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C18" s="2">
         <v>11</v>
       </c>
@@ -2427,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G18" s="1">
         <v>100</v>
@@ -2436,70 +2529,76 @@
         <v>200</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J18" s="8">
         <v>1.4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L18" s="8">
         <v>1.1</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N18" s="8">
         <v>1.65</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P18" s="2">
         <v>1.4</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R18" s="2">
         <v>1.1</v>
       </c>
       <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
         <v>8000</v>
       </c>
-      <c r="T18" s="2">
+      <c r="V18" s="2">
         <v>6000</v>
       </c>
-      <c r="U18" s="2">
+      <c r="W18" s="2">
         <v>25000</v>
       </c>
-      <c r="V18" s="2">
+      <c r="X18" s="2">
         <v>15000</v>
       </c>
-      <c r="W18" s="2">
+      <c r="Y18" s="2">
         <v>400</v>
       </c>
-      <c r="X18" s="2">
+      <c r="Z18" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="AA18" s="2">
         <v>100</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="AB18" s="2">
         <v>0.4</v>
       </c>
-      <c r="AA18" s="2">
+      <c r="AC18" s="2">
         <v>99</v>
       </c>
-      <c r="AB18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC18" s="11" t="s">
-        <v>39</v>
+      <c r="AD18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C19" s="2">
         <v>12</v>
       </c>
@@ -2510,7 +2609,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G19" s="1">
         <v>90</v>
@@ -2519,70 +2618,76 @@
         <v>250</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J19" s="8">
         <v>1.4</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L19" s="8">
         <v>1.1</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N19" s="8">
         <v>1.65</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P19" s="2">
         <v>1.4</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R19" s="2">
         <v>1.1</v>
       </c>
       <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
         <v>8000</v>
       </c>
-      <c r="T19" s="2">
+      <c r="V19" s="2">
         <v>6000</v>
       </c>
-      <c r="U19" s="2">
+      <c r="W19" s="2">
         <v>25000</v>
       </c>
-      <c r="V19" s="2">
+      <c r="X19" s="2">
         <v>15000</v>
       </c>
-      <c r="W19" s="2">
+      <c r="Y19" s="2">
         <v>400</v>
       </c>
-      <c r="X19" s="2">
+      <c r="Z19" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="AA19" s="2">
         <v>100</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="AB19" s="2">
         <v>0.4</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="AC19" s="2">
         <v>99</v>
       </c>
-      <c r="AB19" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC19" s="11" t="s">
-        <v>42</v>
+      <c r="AD19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C20" s="2">
         <v>13</v>
       </c>
@@ -2593,7 +2698,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" s="1">
         <v>80</v>
@@ -2602,70 +2707,76 @@
         <v>300</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J20" s="8">
         <v>1.4</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L20" s="8">
         <v>1.1</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N20" s="8">
         <v>1.65</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P20" s="2">
         <v>1.4</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R20" s="2">
         <v>1.1</v>
       </c>
       <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
         <v>8000</v>
       </c>
-      <c r="T20" s="2">
+      <c r="V20" s="2">
         <v>6000</v>
       </c>
-      <c r="U20" s="2">
+      <c r="W20" s="2">
         <v>25000</v>
       </c>
-      <c r="V20" s="2">
+      <c r="X20" s="2">
         <v>15000</v>
       </c>
-      <c r="W20" s="2">
+      <c r="Y20" s="2">
         <v>400</v>
       </c>
-      <c r="X20" s="2">
+      <c r="Z20" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="AA20" s="2">
         <v>100</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="AB20" s="2">
         <v>0.4</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AC20" s="2">
         <v>99</v>
       </c>
-      <c r="AB20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC20" s="11" t="s">
-        <v>45</v>
+      <c r="AD20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C21" s="2">
         <v>14</v>
       </c>
@@ -2676,7 +2787,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G21" s="1">
         <v>70</v>
@@ -2685,70 +2796,76 @@
         <v>350</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J21" s="8">
         <v>1.4</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L21" s="8">
         <v>1.1</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N21" s="8">
         <v>1.65</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P21" s="2">
         <v>1.4</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R21" s="2">
         <v>1.1</v>
       </c>
       <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
         <v>8000</v>
       </c>
-      <c r="T21" s="2">
+      <c r="V21" s="2">
         <v>6000</v>
       </c>
-      <c r="U21" s="2">
+      <c r="W21" s="2">
         <v>25000</v>
       </c>
-      <c r="V21" s="2">
+      <c r="X21" s="2">
         <v>15000</v>
       </c>
-      <c r="W21" s="2">
+      <c r="Y21" s="2">
         <v>400</v>
       </c>
-      <c r="X21" s="2">
+      <c r="Z21" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="AA21" s="2">
         <v>100</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="AB21" s="2">
         <v>0.4</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AC21" s="2">
         <v>99</v>
       </c>
-      <c r="AB21" s="11" t="s">
+      <c r="AD21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AC21" s="11" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C22" s="2">
         <v>15</v>
       </c>
@@ -2759,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2">
         <v>60</v>
@@ -2768,67 +2885,73 @@
         <v>400</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J22" s="8">
         <v>1.4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L22" s="8">
         <v>1.1</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N22" s="8">
         <v>1.65</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P22" s="2">
         <v>1.4</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R22" s="2">
         <v>1.1</v>
       </c>
       <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
         <v>8000</v>
       </c>
-      <c r="T22" s="2">
+      <c r="V22" s="2">
         <v>6000</v>
       </c>
-      <c r="U22" s="2">
+      <c r="W22" s="2">
         <v>25000</v>
       </c>
-      <c r="V22" s="2">
+      <c r="X22" s="2">
         <v>15000</v>
       </c>
-      <c r="W22" s="2">
+      <c r="Y22" s="2">
         <v>400</v>
       </c>
-      <c r="X22" s="2">
+      <c r="Z22" s="2">
         <v>0.5</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="AA22" s="2">
         <v>100</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AB22" s="2">
         <v>0.4</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AC22" s="2">
         <v>99</v>
       </c>
-      <c r="AB22" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC22" s="11" t="s">
-        <v>50</v>
+      <c r="AD22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="9:14">
@@ -2839,7 +2962,7 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C24" s="2">
         <v>16</v>
       </c>
@@ -2850,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="1">
         <v>100</v>
@@ -2859,70 +2982,76 @@
         <v>300</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J24" s="8">
         <v>1.7</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L24" s="8">
         <v>1.4</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N24" s="8">
         <v>1.8</v>
       </c>
       <c r="O24" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P24" s="2">
         <v>1.7</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R24" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="S24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S24" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="U24" s="2">
         <v>16000</v>
       </c>
-      <c r="T24" s="2">
+      <c r="V24" s="2">
         <v>12000</v>
       </c>
-      <c r="U24" s="2">
+      <c r="W24" s="2">
         <v>40000</v>
       </c>
-      <c r="V24" s="2">
+      <c r="X24" s="2">
         <v>30000</v>
       </c>
-      <c r="W24" s="2">
+      <c r="Y24" s="2">
         <v>600</v>
       </c>
-      <c r="X24" s="2">
+      <c r="Z24" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y24" s="2">
+      <c r="AA24" s="2">
         <v>200</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="AB24" s="2">
         <v>0.5</v>
       </c>
-      <c r="AA24" s="2">
+      <c r="AC24" s="2">
         <v>99</v>
       </c>
-      <c r="AB24" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC24" s="11" t="s">
-        <v>75</v>
+      <c r="AD24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C25" s="2">
         <v>17</v>
       </c>
@@ -2933,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G25" s="1">
         <v>90</v>
@@ -2942,70 +3071,76 @@
         <v>300</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J25" s="8">
         <v>1.7</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L25" s="8">
         <v>1.4</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N25" s="8">
         <v>1.8</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P25" s="2">
         <v>1.7</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R25" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="S25" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T25" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="U25" s="2">
         <v>16000</v>
       </c>
-      <c r="T25" s="2">
+      <c r="V25" s="2">
         <v>12000</v>
       </c>
-      <c r="U25" s="2">
+      <c r="W25" s="2">
         <v>40000</v>
       </c>
-      <c r="V25" s="2">
+      <c r="X25" s="2">
         <v>30000</v>
       </c>
-      <c r="W25" s="2">
+      <c r="Y25" s="2">
         <v>600</v>
       </c>
-      <c r="X25" s="2">
+      <c r="Z25" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="AA25" s="2">
         <v>200</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="AB25" s="2">
         <v>0.5</v>
       </c>
-      <c r="AA25" s="2">
+      <c r="AC25" s="2">
         <v>99</v>
       </c>
-      <c r="AB25" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC25" s="11" t="s">
-        <v>50</v>
+      <c r="AD25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C26" s="2">
         <v>18</v>
       </c>
@@ -3016,7 +3151,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G26" s="1">
         <v>80</v>
@@ -3025,70 +3160,76 @@
         <v>400</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J26" s="8">
         <v>1.7</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L26" s="8">
         <v>1.4</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N26" s="8">
         <v>1.8</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P26" s="2">
         <v>1.7</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R26" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="S26" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S26" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="U26" s="2">
         <v>16000</v>
       </c>
-      <c r="T26" s="2">
+      <c r="V26" s="2">
         <v>12000</v>
       </c>
-      <c r="U26" s="2">
+      <c r="W26" s="2">
         <v>40000</v>
       </c>
-      <c r="V26" s="2">
+      <c r="X26" s="2">
         <v>30000</v>
       </c>
-      <c r="W26" s="2">
+      <c r="Y26" s="2">
         <v>600</v>
       </c>
-      <c r="X26" s="2">
+      <c r="Z26" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="AA26" s="2">
         <v>200</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="AB26" s="2">
         <v>0.5</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AC26" s="2">
         <v>99</v>
       </c>
-      <c r="AB26" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC26" s="11" t="s">
-        <v>80</v>
+      <c r="AD26" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C27" s="2">
         <v>19</v>
       </c>
@@ -3099,7 +3240,7 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G27" s="1">
         <v>70</v>
@@ -3108,70 +3249,76 @@
         <v>400</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J27" s="8">
         <v>1.7</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L27" s="8">
         <v>1.4</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N27" s="8">
         <v>1.8</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P27" s="2">
         <v>1.7</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R27" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="S27" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S27" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T27" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="U27" s="2">
         <v>16000</v>
       </c>
-      <c r="T27" s="2">
+      <c r="V27" s="2">
         <v>12000</v>
       </c>
-      <c r="U27" s="2">
+      <c r="W27" s="2">
         <v>40000</v>
       </c>
-      <c r="V27" s="2">
+      <c r="X27" s="2">
         <v>30000</v>
       </c>
-      <c r="W27" s="2">
+      <c r="Y27" s="2">
         <v>600</v>
       </c>
-      <c r="X27" s="2">
+      <c r="Z27" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y27" s="2">
+      <c r="AA27" s="2">
         <v>200</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="AB27" s="2">
         <v>0.5</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="AC27" s="2">
         <v>99</v>
       </c>
-      <c r="AB27" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC27" s="11" t="s">
-        <v>83</v>
+      <c r="AD27" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:29">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:31">
       <c r="C28" s="2">
         <v>20</v>
       </c>
@@ -3182,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G28" s="2">
         <v>60</v>
@@ -3191,67 +3338,73 @@
         <v>400</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J28" s="8">
         <v>1.7</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L28" s="8">
         <v>1.4</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N28" s="8">
         <v>1.8</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P28" s="2">
         <v>1.7</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R28" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="S28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="S28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="U28" s="2">
         <v>16000</v>
       </c>
-      <c r="T28" s="2">
+      <c r="V28" s="2">
         <v>12000</v>
       </c>
-      <c r="U28" s="2">
+      <c r="W28" s="2">
         <v>40000</v>
       </c>
-      <c r="V28" s="2">
+      <c r="X28" s="2">
         <v>30000</v>
       </c>
-      <c r="W28" s="2">
+      <c r="Y28" s="2">
         <v>600</v>
       </c>
-      <c r="X28" s="2">
+      <c r="Z28" s="2">
         <v>0.6</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="AA28" s="2">
         <v>200</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="AB28" s="2">
         <v>0.5</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="AC28" s="2">
         <v>99</v>
       </c>
-      <c r="AB28" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC28" s="11" t="s">
-        <v>86</v>
+      <c r="AD28" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="9:14">
@@ -3262,9 +3415,23 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
+    <row r="31" customHeight="1" spans="1:18">
+      <c r="A31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="R31" s="2">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AC5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AE5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -3009,7 +3009,7 @@
         <v>75</v>
       </c>
       <c r="R24" s="2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S24" s="13" t="s">
         <v>76</v>
@@ -3098,7 +3098,7 @@
         <v>75</v>
       </c>
       <c r="R25" s="2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S25" s="13" t="s">
         <v>76</v>
@@ -3187,7 +3187,7 @@
         <v>75</v>
       </c>
       <c r="R26" s="2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S26" s="13" t="s">
         <v>76</v>
@@ -3276,7 +3276,7 @@
         <v>75</v>
       </c>
       <c r="R27" s="2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S27" s="13" t="s">
         <v>76</v>
@@ -3365,7 +3365,7 @@
         <v>75</v>
       </c>
       <c r="R28" s="2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S28" s="13" t="s">
         <v>76</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -302,10 +302,31 @@
     <t>20,20,20,20,20,20,20,20,20</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1E+30</t>
+    <t>麒麟</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+80</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+60</t>
+  </si>
+  <si>
+    <t>麒麟幻象</t>
+  </si>
+  <si>
+    <t>麒麟分身</t>
+  </si>
+  <si>
+    <t>麒麟法相</t>
+  </si>
+  <si>
+    <t>麒麟化身</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE31"/>
+  <dimension ref="C1:AE39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -1328,11 +1349,11 @@
     <col min="16318" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:4">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
@@ -2048,7 +2069,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="9:14">
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:31">
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
@@ -2501,7 +2522,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="9:14">
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:31">
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
@@ -2954,7 +2975,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="9:14">
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:31">
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -3407,7 +3428,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="9:14">
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:31">
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
@@ -3415,19 +3436,531 @@
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
     </row>
-    <row r="31" customHeight="1" spans="1:18">
-      <c r="A31" s="1" t="s">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C30" s="2">
+        <v>21</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="G30" s="1">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>300</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="8">
+        <v>2</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30" s="8">
+        <v>2</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N30" s="8">
+        <v>2</v>
+      </c>
+      <c r="O30" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P30" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R30" s="2">
+        <v>2</v>
+      </c>
+      <c r="S30" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T30" s="2">
+        <v>2</v>
+      </c>
+      <c r="U30" s="2">
+        <v>100000</v>
+      </c>
+      <c r="V30" s="2">
+        <v>100000</v>
+      </c>
+      <c r="W30" s="2">
+        <v>100000</v>
+      </c>
+      <c r="X30" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>400</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC30" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE30" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C31" s="2">
+        <v>22</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="1">
         <v>90</v>
       </c>
+      <c r="H31" s="1">
+        <v>300</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J31" s="8">
+        <v>2</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L31" s="8">
+        <v>2</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N31" s="8">
+        <v>2</v>
+      </c>
+      <c r="O31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P31" s="2">
+        <v>2</v>
+      </c>
       <c r="Q31" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R31" s="2">
+        <v>2</v>
+      </c>
+      <c r="S31" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T31" s="2">
+        <v>2</v>
+      </c>
+      <c r="U31" s="2">
+        <v>100000</v>
+      </c>
+      <c r="V31" s="2">
+        <v>100000</v>
+      </c>
+      <c r="W31" s="2">
+        <v>100000</v>
+      </c>
+      <c r="X31" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>400</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE31" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C32" s="2">
+        <v>23</v>
+      </c>
+      <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="1">
+        <v>80</v>
+      </c>
+      <c r="H32" s="2">
+        <v>400</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="R31" s="2">
-        <v>1.6</v>
-      </c>
+      <c r="J32" s="8">
+        <v>2</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L32" s="8">
+        <v>2</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N32" s="8">
+        <v>2</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R32" s="2">
+        <v>2</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T32" s="2">
+        <v>2</v>
+      </c>
+      <c r="U32" s="2">
+        <v>100000</v>
+      </c>
+      <c r="V32" s="2">
+        <v>100000</v>
+      </c>
+      <c r="W32" s="2">
+        <v>100000</v>
+      </c>
+      <c r="X32" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>400</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE32" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C33" s="2">
+        <v>24</v>
+      </c>
+      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="1">
+        <v>70</v>
+      </c>
+      <c r="H33" s="2">
+        <v>400</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="8">
+        <v>2</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N33" s="8">
+        <v>2</v>
+      </c>
+      <c r="O33" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P33" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R33" s="2">
+        <v>2</v>
+      </c>
+      <c r="S33" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T33" s="2">
+        <v>2</v>
+      </c>
+      <c r="U33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="V33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="W33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="X33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Z33" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>400</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC33" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD33" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE33" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C34" s="2">
+        <v>25</v>
+      </c>
+      <c r="D34" s="2">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>5</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="2">
+        <v>60</v>
+      </c>
+      <c r="H34" s="2">
+        <v>400</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="8">
+        <v>2</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L34" s="8">
+        <v>2</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N34" s="8">
+        <v>2</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P34" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R34" s="2">
+        <v>2</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="T34" s="2">
+        <v>2</v>
+      </c>
+      <c r="U34" s="2">
+        <v>100000</v>
+      </c>
+      <c r="V34" s="2">
+        <v>100000</v>
+      </c>
+      <c r="W34" s="2">
+        <v>100000</v>
+      </c>
+      <c r="X34" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Y34" s="2">
+        <v>1000</v>
+      </c>
+      <c r="Z34" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>400</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC34" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE34" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="9"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="9"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="9"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="9"/>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="100">
   <si>
     <t>ID</t>
   </si>
@@ -305,16 +305,19 @@
     <t>麒麟</t>
   </si>
   <si>
-    <t>1E+100</t>
+    <t>1E+90</t>
   </si>
   <si>
     <t>1E+80</t>
   </si>
   <si>
-    <t>1E+120</t>
-  </si>
-  <si>
-    <t>1E+60</t>
+    <t>1E+96</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>2003,1008,1012,2009</t>
   </si>
   <si>
     <t>麒麟幻象</t>
@@ -3459,37 +3462,37 @@
         <v>91</v>
       </c>
       <c r="J30" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K30" s="12" t="s">
         <v>92</v>
       </c>
       <c r="L30" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>93</v>
       </c>
       <c r="N30" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O30" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="P30" s="2">
-        <v>2</v>
+      <c r="P30" s="8">
+        <v>1.8</v>
       </c>
       <c r="Q30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R30" s="2">
-        <v>2</v>
+      <c r="R30" s="8">
+        <v>1.8</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T30" s="2">
-        <v>2</v>
+      <c r="T30" s="8">
+        <v>1.8</v>
       </c>
       <c r="U30" s="2">
         <v>100000</v>
@@ -3519,7 +3522,7 @@
         <v>99</v>
       </c>
       <c r="AD30" s="11" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AE30" s="11" t="s">
         <v>78</v>
@@ -3536,7 +3539,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G31" s="1">
         <v>90</v>
@@ -3545,40 +3548,40 @@
         <v>300</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J31" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K31" s="12" t="s">
         <v>92</v>
       </c>
       <c r="L31" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>93</v>
       </c>
       <c r="N31" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O31" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="P31" s="2">
-        <v>2</v>
+      <c r="P31" s="8">
+        <v>1.8</v>
       </c>
       <c r="Q31" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R31" s="2">
-        <v>2</v>
+      <c r="R31" s="8">
+        <v>1.8</v>
       </c>
       <c r="S31" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T31" s="2">
-        <v>2</v>
+      <c r="T31" s="8">
+        <v>1.8</v>
       </c>
       <c r="U31" s="2">
         <v>100000</v>
@@ -3625,7 +3628,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G32" s="1">
         <v>80</v>
@@ -3634,40 +3637,40 @@
         <v>400</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J32" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K32" s="12" t="s">
         <v>92</v>
       </c>
       <c r="L32" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="13" t="s">
         <v>93</v>
       </c>
       <c r="N32" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="P32" s="2">
-        <v>2</v>
+      <c r="P32" s="8">
+        <v>1.8</v>
       </c>
       <c r="Q32" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R32" s="2">
-        <v>2</v>
+      <c r="R32" s="8">
+        <v>1.8</v>
       </c>
       <c r="S32" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T32" s="2">
-        <v>2</v>
+      <c r="T32" s="8">
+        <v>1.8</v>
       </c>
       <c r="U32" s="2">
         <v>100000</v>
@@ -3714,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G33" s="1">
         <v>70</v>
@@ -3723,40 +3726,40 @@
         <v>400</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J33" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="12" t="s">
         <v>92</v>
       </c>
       <c r="L33" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>93</v>
       </c>
       <c r="N33" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="P33" s="2">
-        <v>2</v>
+      <c r="P33" s="8">
+        <v>1.8</v>
       </c>
       <c r="Q33" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R33" s="2">
-        <v>2</v>
+      <c r="R33" s="8">
+        <v>1.8</v>
       </c>
       <c r="S33" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T33" s="2">
-        <v>2</v>
+      <c r="T33" s="8">
+        <v>1.8</v>
       </c>
       <c r="U33" s="2">
         <v>100000</v>
@@ -3803,7 +3806,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G34" s="2">
         <v>60</v>
@@ -3812,40 +3815,40 @@
         <v>400</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J34" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K34" s="12" t="s">
         <v>92</v>
       </c>
       <c r="L34" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M34" s="13" t="s">
         <v>93</v>
       </c>
       <c r="N34" s="8">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O34" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="P34" s="2">
-        <v>2</v>
+      <c r="P34" s="8">
+        <v>1.8</v>
       </c>
       <c r="Q34" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R34" s="2">
-        <v>2</v>
+      <c r="R34" s="8">
+        <v>1.8</v>
       </c>
       <c r="S34" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T34" s="2">
-        <v>2</v>
+      <c r="T34" s="8">
+        <v>1.8</v>
       </c>
       <c r="U34" s="2">
         <v>100000</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="101">
   <si>
     <t>ID</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+35</t>
   </si>
   <si>
     <t>2003,1008,1012,2009</t>
@@ -3483,16 +3486,16 @@
         <v>1.8</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="R30" s="8">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>74</v>
       </c>
       <c r="T30" s="8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U30" s="2">
         <v>100000</v>
@@ -3522,7 +3525,7 @@
         <v>99</v>
       </c>
       <c r="AD30" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE30" s="11" t="s">
         <v>78</v>
@@ -3539,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G31" s="1">
         <v>90</v>
@@ -3572,16 +3575,16 @@
         <v>1.8</v>
       </c>
       <c r="Q31" s="13" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="R31" s="8">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S31" s="13" t="s">
         <v>74</v>
       </c>
       <c r="T31" s="8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U31" s="2">
         <v>100000</v>
@@ -3628,7 +3631,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G32" s="1">
         <v>80</v>
@@ -3661,16 +3664,16 @@
         <v>1.8</v>
       </c>
       <c r="Q32" s="13" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="R32" s="8">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S32" s="13" t="s">
         <v>74</v>
       </c>
       <c r="T32" s="8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U32" s="2">
         <v>100000</v>
@@ -3717,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G33" s="1">
         <v>70</v>
@@ -3750,16 +3753,16 @@
         <v>1.8</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="R33" s="8">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S33" s="13" t="s">
         <v>74</v>
       </c>
       <c r="T33" s="8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U33" s="2">
         <v>100000</v>
@@ -3806,7 +3809,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G34" s="2">
         <v>60</v>
@@ -3839,16 +3842,16 @@
         <v>1.8</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="R34" s="8">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S34" s="13" t="s">
         <v>74</v>
       </c>
       <c r="T34" s="8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U34" s="2">
         <v>100000</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="109">
   <si>
     <t>ID</t>
   </si>
@@ -333,6 +333,30 @@
   </si>
   <si>
     <t>麒麟化身</t>
+  </si>
+  <si>
+    <t>极·青龙</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>极·青龙幻象</t>
+  </si>
+  <si>
+    <t>极·青龙分身</t>
+  </si>
+  <si>
+    <t>极·青龙法相</t>
+  </si>
+  <si>
+    <t>极·青龙化身</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1346,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AE39"/>
+  <dimension ref="C1:AE42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -3887,87 +3911,460 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:31">
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="9"/>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:31">
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:31">
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="9"/>
+      <c r="C36" s="2">
+        <v>26</v>
+      </c>
+      <c r="D36" s="2">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="1">
+        <v>100</v>
+      </c>
+      <c r="H36" s="1">
+        <v>400</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" s="8">
+        <v>1</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N36" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q36" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S36" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T36" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U36" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V36" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W36" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X36" s="2">
+        <v>200000</v>
+      </c>
+      <c r="Y36" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD36" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE36" s="11" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:31">
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="9"/>
+      <c r="C37" s="2">
+        <v>27</v>
+      </c>
+      <c r="D37" s="2">
+        <v>6</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="1">
+        <v>90</v>
+      </c>
+      <c r="H37" s="1">
+        <v>400</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L37" s="8">
+        <v>1</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N37" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P37" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R37" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S37" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T37" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U37" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V37" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W37" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X37" s="2">
+        <v>200000</v>
+      </c>
+      <c r="Y37" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Z37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD37" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE37" s="11" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:31">
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="9"/>
+      <c r="C38" s="2">
+        <v>28</v>
+      </c>
+      <c r="D38" s="2">
+        <v>6</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="1">
+        <v>80</v>
+      </c>
+      <c r="H38" s="1">
+        <v>400</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L38" s="8">
+        <v>1</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N38" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P38" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R38" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S38" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T38" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U38" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V38" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W38" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X38" s="2">
+        <v>200000</v>
+      </c>
+      <c r="Y38" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB38" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD38" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE38" s="11" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:31">
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="9"/>
+      <c r="C39" s="2">
+        <v>29</v>
+      </c>
+      <c r="D39" s="2">
+        <v>6</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G39" s="1">
+        <v>70</v>
+      </c>
+      <c r="H39" s="1">
+        <v>400</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J39" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L39" s="8">
+        <v>1</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N39" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P39" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S39" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T39" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="Y39" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Z39" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB39" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD39" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE39" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C40" s="2">
+        <v>30</v>
+      </c>
+      <c r="D40" s="2">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G40" s="2">
+        <v>60</v>
+      </c>
+      <c r="H40" s="1">
+        <v>400</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L40" s="8">
+        <v>1</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N40" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P40" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R40" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S40" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T40" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U40" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V40" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W40" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X40" s="2">
+        <v>200000</v>
+      </c>
+      <c r="Y40" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>600</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD40" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE40" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AE5" errorStyle="warning">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -3942,7 +3942,7 @@
         <v>102</v>
       </c>
       <c r="J36" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K36" s="12" t="s">
         <v>102</v>
@@ -3954,13 +3954,13 @@
         <v>103</v>
       </c>
       <c r="N36" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>102</v>
       </c>
       <c r="P36" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="13" t="s">
         <v>104</v>
@@ -3972,7 +3972,7 @@
         <v>104</v>
       </c>
       <c r="T36" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U36" s="2">
         <v>200000</v>
@@ -4031,7 +4031,7 @@
         <v>102</v>
       </c>
       <c r="J37" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K37" s="12" t="s">
         <v>102</v>
@@ -4043,13 +4043,13 @@
         <v>103</v>
       </c>
       <c r="N37" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="s">
         <v>102</v>
       </c>
       <c r="P37" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="13" t="s">
         <v>104</v>
@@ -4061,7 +4061,7 @@
         <v>104</v>
       </c>
       <c r="T37" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U37" s="2">
         <v>200000</v>
@@ -4120,7 +4120,7 @@
         <v>102</v>
       </c>
       <c r="J38" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K38" s="12" t="s">
         <v>102</v>
@@ -4132,13 +4132,13 @@
         <v>103</v>
       </c>
       <c r="N38" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O38" s="12" t="s">
         <v>102</v>
       </c>
       <c r="P38" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="13" t="s">
         <v>104</v>
@@ -4150,7 +4150,7 @@
         <v>104</v>
       </c>
       <c r="T38" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U38" s="2">
         <v>200000</v>
@@ -4209,7 +4209,7 @@
         <v>102</v>
       </c>
       <c r="J39" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K39" s="12" t="s">
         <v>102</v>
@@ -4221,13 +4221,13 @@
         <v>103</v>
       </c>
       <c r="N39" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>102</v>
       </c>
       <c r="P39" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="13" t="s">
         <v>104</v>
@@ -4239,7 +4239,7 @@
         <v>104</v>
       </c>
       <c r="T39" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U39" s="2">
         <v>200000</v>
@@ -4298,7 +4298,7 @@
         <v>102</v>
       </c>
       <c r="J40" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K40" s="12" t="s">
         <v>102</v>
@@ -4310,13 +4310,13 @@
         <v>103</v>
       </c>
       <c r="N40" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O40" s="12" t="s">
         <v>102</v>
       </c>
       <c r="P40" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="13" t="s">
         <v>104</v>
@@ -4328,7 +4328,7 @@
         <v>104</v>
       </c>
       <c r="T40" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U40" s="2">
         <v>200000</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
   <si>
     <t>ID</t>
   </si>
@@ -338,13 +338,16 @@
     <t>极·青龙</t>
   </si>
   <si>
+    <t>1E+120</t>
+  </si>
+  <si>
     <t>1E+100</t>
   </si>
   <si>
-    <t>1E+120</t>
-  </si>
-  <si>
-    <t>1E+50</t>
+    <t>1E+130</t>
+  </si>
+  <si>
+    <t>1E+60</t>
   </si>
   <si>
     <t>极·青龙幻象</t>
@@ -3945,31 +3948,31 @@
         <v>2</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L36" s="8">
         <v>1</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N36" s="8">
         <v>2</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P36" s="2">
         <v>2</v>
       </c>
       <c r="Q36" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R36" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S36" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T36" s="2">
         <v>2</v>
@@ -4019,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G37" s="1">
         <v>90</v>
@@ -4034,31 +4037,31 @@
         <v>2</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N37" s="8">
         <v>2</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P37" s="2">
         <v>2</v>
       </c>
       <c r="Q37" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R37" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S37" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T37" s="2">
         <v>2</v>
@@ -4108,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G38" s="1">
         <v>80</v>
@@ -4123,31 +4126,31 @@
         <v>2</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L38" s="8">
         <v>1</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N38" s="8">
         <v>2</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P38" s="2">
         <v>2</v>
       </c>
       <c r="Q38" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R38" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S38" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T38" s="2">
         <v>2</v>
@@ -4197,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G39" s="1">
         <v>70</v>
@@ -4212,31 +4215,31 @@
         <v>2</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L39" s="8">
         <v>1</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N39" s="8">
         <v>2</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P39" s="2">
         <v>2</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R39" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T39" s="2">
         <v>2</v>
@@ -4286,7 +4289,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G40" s="2">
         <v>60</v>
@@ -4301,31 +4304,31 @@
         <v>2</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N40" s="8">
         <v>2</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P40" s="2">
         <v>2</v>
       </c>
       <c r="Q40" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R40" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S40" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T40" s="2">
         <v>2</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -3537,7 +3537,7 @@
         <v>100000</v>
       </c>
       <c r="Y30" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Z30" s="2">
         <v>1</v>
@@ -3626,7 +3626,7 @@
         <v>100000</v>
       </c>
       <c r="Y31" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Z31" s="2">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>100000</v>
       </c>
       <c r="Y32" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Z32" s="2">
         <v>1</v>
@@ -3804,7 +3804,7 @@
         <v>100000</v>
       </c>
       <c r="Y33" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Z33" s="2">
         <v>1</v>
@@ -3893,7 +3893,7 @@
         <v>100000</v>
       </c>
       <c r="Y34" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Z34" s="2">
         <v>1</v>
@@ -3990,13 +3990,13 @@
         <v>200000</v>
       </c>
       <c r="Y36" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z36" s="2">
         <v>1</v>
       </c>
       <c r="AA36" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB36" s="2">
         <v>1</v>
@@ -4079,13 +4079,13 @@
         <v>200000</v>
       </c>
       <c r="Y37" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z37" s="2">
         <v>1</v>
       </c>
       <c r="AA37" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB37" s="2">
         <v>1</v>
@@ -4168,13 +4168,13 @@
         <v>200000</v>
       </c>
       <c r="Y38" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z38" s="2">
         <v>1</v>
       </c>
       <c r="AA38" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB38" s="2">
         <v>1</v>
@@ -4257,13 +4257,13 @@
         <v>200000</v>
       </c>
       <c r="Y39" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z39" s="2">
         <v>1</v>
       </c>
       <c r="AA39" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB39" s="2">
         <v>1</v>
@@ -4346,13 +4346,13 @@
         <v>200000</v>
       </c>
       <c r="Y40" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="Z40" s="2">
         <v>1</v>
       </c>
       <c r="AA40" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB40" s="2">
         <v>1</v>

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -356,10 +356,34 @@
     <t>极·青龙分身</t>
   </si>
   <si>
+    <t>2002,2007,2008,2009,1008</t>
+  </si>
+  <si>
     <t>极·青龙法相</t>
   </si>
   <si>
     <t>极·青龙化身</t>
+  </si>
+  <si>
+    <t>极·白虎</t>
+  </si>
+  <si>
+    <t>1E+160</t>
+  </si>
+  <si>
+    <t>1E+170</t>
+  </si>
+  <si>
+    <t>极·白虎幻象</t>
+  </si>
+  <si>
+    <t>极·白虎分身</t>
+  </si>
+  <si>
+    <t>极·白虎法相</t>
+  </si>
+  <si>
+    <t>极·白虎化身</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AE42"/>
+  <dimension ref="C1:AE46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -1376,7 +1400,7 @@
     <col min="26" max="26" width="8.76666666666667" style="1" customWidth="1"/>
     <col min="27" max="28" width="9.25" style="1" customWidth="1"/>
     <col min="29" max="29" width="9.375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="26.5" style="1" customWidth="1"/>
+    <col min="30" max="30" width="31.6666666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="14" style="1" customWidth="1"/>
     <col min="32" max="16317" width="9" style="1"/>
     <col min="16318" max="16384" width="9" style="5"/>
@@ -3996,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="AA36" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AB36" s="2">
         <v>1</v>
@@ -4085,7 +4109,7 @@
         <v>1</v>
       </c>
       <c r="AA37" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AB37" s="2">
         <v>1</v>
@@ -4174,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="AA38" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AB38" s="2">
         <v>1</v>
@@ -4183,7 +4207,7 @@
         <v>99</v>
       </c>
       <c r="AD38" s="11" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AE38" s="11" t="s">
         <v>83</v>
@@ -4200,7 +4224,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G39" s="1">
         <v>70</v>
@@ -4263,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="AA39" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AB39" s="2">
         <v>1</v>
@@ -4289,7 +4313,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G40" s="2">
         <v>60</v>
@@ -4352,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="AA40" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AB40" s="2">
         <v>1</v>
@@ -4367,7 +4391,451 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" ht="13" customHeight="1"/>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C42" s="2">
+        <v>31</v>
+      </c>
+      <c r="D42" s="2">
+        <v>7</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="1">
+        <v>100</v>
+      </c>
+      <c r="H42" s="1">
+        <v>400</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J42" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L42" s="8">
+        <v>1</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N42" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="P42" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R42" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="T42" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="U42" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V42" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W42" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X42" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>500</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD42" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE42" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C43" s="2">
+        <v>32</v>
+      </c>
+      <c r="D43" s="2">
+        <v>7</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="1">
+        <v>90</v>
+      </c>
+      <c r="H43" s="1">
+        <v>400</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J43" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L43" s="8">
+        <v>1</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N43" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R43" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S43" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="T43" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="U43" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V43" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W43" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X43" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y43" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>500</v>
+      </c>
+      <c r="AB43" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD43" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE43" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C44" s="2">
+        <v>33</v>
+      </c>
+      <c r="D44" s="2">
+        <v>7</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="1">
+        <v>80</v>
+      </c>
+      <c r="H44" s="1">
+        <v>400</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J44" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L44" s="8">
+        <v>1</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N44" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="P44" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R44" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S44" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="T44" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="U44" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V44" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W44" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X44" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="2">
+        <v>500</v>
+      </c>
+      <c r="AB44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD44" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE44" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C45" s="2">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G45" s="1">
+        <v>70</v>
+      </c>
+      <c r="H45" s="1">
+        <v>400</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J45" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L45" s="8">
+        <v>1</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N45" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="O45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q45" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R45" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S45" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="T45" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="U45" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V45" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W45" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X45" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y45" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="2">
+        <v>500</v>
+      </c>
+      <c r="AB45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD45" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE45" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C46" s="2">
+        <v>35</v>
+      </c>
+      <c r="D46" s="2">
+        <v>7</v>
+      </c>
+      <c r="E46" s="2">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="2">
+        <v>60</v>
+      </c>
+      <c r="H46" s="1">
+        <v>400</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J46" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L46" s="8">
+        <v>1</v>
+      </c>
+      <c r="M46" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N46" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="O46" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="P46" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q46" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="R46" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S46" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="T46" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="U46" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V46" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W46" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X46" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y46" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>500</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD46" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE46" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AE5" errorStyle="warning">

--- a/Excel/MonsterWorldConfig.xlsx
+++ b/Excel/MonsterWorldConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -384,6 +389,24 @@
   </si>
   <si>
     <t>极·白虎化身</t>
+  </si>
+  <si>
+    <t>极·朱雀</t>
+  </si>
+  <si>
+    <t>1E+200</t>
+  </si>
+  <si>
+    <t>极·朱雀幻象</t>
+  </si>
+  <si>
+    <t>极·朱雀分身</t>
+  </si>
+  <si>
+    <t>极·朱雀法相</t>
+  </si>
+  <si>
+    <t>极·朱雀化身</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AE46"/>
+  <dimension ref="C1:AE52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
@@ -4836,6 +4859,451 @@
         <v>89</v>
       </c>
     </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C48" s="2">
+        <v>36</v>
+      </c>
+      <c r="D48" s="2">
+        <v>8</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="1">
+        <v>100</v>
+      </c>
+      <c r="H48" s="1">
+        <v>400</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J48" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L48" s="8">
+        <v>1</v>
+      </c>
+      <c r="M48" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N48" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O48" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P48" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q48" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R48" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S48" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T48" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U48" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V48" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W48" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X48" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>550</v>
+      </c>
+      <c r="AB48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD48" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE48" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C49" s="2">
+        <v>37</v>
+      </c>
+      <c r="D49" s="2">
+        <v>8</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G49" s="1">
+        <v>90</v>
+      </c>
+      <c r="H49" s="1">
+        <v>400</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J49" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L49" s="8">
+        <v>1</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N49" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O49" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P49" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q49" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R49" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S49" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T49" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U49" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V49" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W49" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X49" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z49" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="2">
+        <v>550</v>
+      </c>
+      <c r="AB49" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD49" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE49" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C50" s="2">
+        <v>38</v>
+      </c>
+      <c r="D50" s="2">
+        <v>8</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G50" s="1">
+        <v>80</v>
+      </c>
+      <c r="H50" s="1">
+        <v>400</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J50" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L50" s="8">
+        <v>1</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N50" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P50" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q50" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R50" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S50" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T50" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U50" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V50" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W50" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X50" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="2">
+        <v>550</v>
+      </c>
+      <c r="AB50" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD50" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE50" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C51" s="2">
+        <v>39</v>
+      </c>
+      <c r="D51" s="2">
+        <v>8</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G51" s="1">
+        <v>70</v>
+      </c>
+      <c r="H51" s="1">
+        <v>400</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J51" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L51" s="8">
+        <v>1</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N51" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O51" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P51" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q51" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S51" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T51" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U51" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V51" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W51" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X51" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z51" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="2">
+        <v>550</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD51" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE51" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:31">
+      <c r="C52" s="2">
+        <v>40</v>
+      </c>
+      <c r="D52" s="2">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2">
+        <v>5</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" s="2">
+        <v>60</v>
+      </c>
+      <c r="H52" s="1">
+        <v>400</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J52" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52" s="8">
+        <v>1</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N52" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O52" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="P52" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="Q52" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R52" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="S52" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T52" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="U52" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V52" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W52" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X52" s="2">
+        <v>400000</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>1200</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>550</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>99</v>
+      </c>
+      <c r="AD52" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE52" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AE5" errorStyle="warning">
